--- a/templates/insurance/社保分单位模板.xlsx
+++ b/templates/insurance/社保分单位模板.xlsx
@@ -439,16 +439,11 @@
           <t>已参保</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>转款金额</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -608,6 +603,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="G2:I2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>